--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:Q92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5843,10 +5843,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H86" t="n">
+        <v>1.5</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5908,10 +5906,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H87" t="n">
+        <v>1.5</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5937,6 +5933,331 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:45:10</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>3.7841</v>
+      </c>
+      <c r="K88" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Sportybet, Betway</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:45:10</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>0.5414</v>
+      </c>
+      <c r="K89" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:45:10</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>2.3113</v>
+      </c>
+      <c r="K90" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Football.com, Betway</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:45:10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K91" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L91" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:45:10</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K92" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L92" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q92"/>
+  <dimension ref="A1:Q97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5969,10 +5969,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H88" t="n">
+        <v>1.5</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -6034,10 +6032,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H89" t="n">
+        <v>1.5</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -6099,10 +6095,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H90" t="n">
+        <v>1.5</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -6164,10 +6158,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H91" t="n">
+        <v>4.5</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -6229,10 +6221,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H92" t="n">
+        <v>4.5</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -6258,6 +6248,331 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:47:27</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K93" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L93" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:47:27</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K94" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L94" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:47:27</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>3.7841</v>
+      </c>
+      <c r="K95" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Sportybet, Betway</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:47:27</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>0.5414</v>
+      </c>
+      <c r="K96" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:47:27</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>2.3113</v>
+      </c>
+      <c r="K97" t="n">
+        <v>27.62</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Football.com, Betway</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q97"/>
+  <dimension ref="A1:Q103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6284,10 +6284,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H93" t="n">
+        <v>4.5</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -6349,10 +6347,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H94" t="n">
+        <v>4.5</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -6414,10 +6410,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H95" t="n">
+        <v>1.5</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -6479,10 +6473,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H96" t="n">
+        <v>1.5</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -6544,10 +6536,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H97" t="n">
+        <v>1.5</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -6573,6 +6563,396 @@
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:49:42</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K98" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L98" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:49:42</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K99" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L99" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:49:42</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>5.4059</v>
+      </c>
+      <c r="K100" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Sportybet, Betway</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:49:42</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>2.1632</v>
+      </c>
+      <c r="K101" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:49:42</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>3.9105</v>
+      </c>
+      <c r="K102" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Football.com, Betway</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:49:42</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="K103" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Football.com, Bangbet</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q103"/>
+  <dimension ref="A1:Q109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6599,10 +6599,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H98" t="n">
+        <v>4.5</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -6664,10 +6662,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H99" t="n">
+        <v>4.5</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -6729,10 +6725,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H100" t="n">
+        <v>1.5</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6794,10 +6788,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H101" t="n">
+        <v>1.5</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -6859,10 +6851,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H102" t="n">
+        <v>1.5</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6924,10 +6914,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H103" t="n">
+        <v>1.5</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -6953,6 +6941,396 @@
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:51:53</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K104" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L104" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:51:53</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K105" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L105" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:51:53</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>5.4059</v>
+      </c>
+      <c r="K106" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Sportybet, Betway</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:51:53</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>2.1632</v>
+      </c>
+      <c r="K107" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:51:53</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>3.9105</v>
+      </c>
+      <c r="K108" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Football.com, Betway</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:51:53</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="K109" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Football.com, Bangbet</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q109"/>
+  <dimension ref="A1:Q115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6977,10 +6977,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H104" t="n">
+        <v>4.5</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -7042,10 +7040,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H105" t="n">
+        <v>4.5</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -7107,10 +7103,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H106" t="n">
+        <v>1.5</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -7172,10 +7166,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H107" t="n">
+        <v>1.5</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -7237,10 +7229,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H108" t="n">
+        <v>1.5</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -7302,10 +7292,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H109" t="n">
+        <v>1.5</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -7331,6 +7319,396 @@
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:54:03</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K110" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L110" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:54:03</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K111" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L111" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:54:03</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>5.4059</v>
+      </c>
+      <c r="K112" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Sportybet, Betway</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:54:03</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>2.1632</v>
+      </c>
+      <c r="K113" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:54:03</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>3.9105</v>
+      </c>
+      <c r="K114" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Football.com, Betway</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:54:03</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="K115" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Football.com, Bangbet</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q115"/>
+  <dimension ref="A1:Q121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7355,10 +7355,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H110" t="n">
+        <v>4.5</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -7420,10 +7418,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H111" t="n">
+        <v>4.5</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -7485,10 +7481,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H112" t="n">
+        <v>1.5</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -7550,10 +7544,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H113" t="n">
+        <v>1.5</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -7615,10 +7607,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H114" t="n">
+        <v>1.5</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -7680,10 +7670,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H115" t="n">
+        <v>1.5</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -7709,6 +7697,396 @@
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:56:12</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K116" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L116" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:56:12</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K117" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L117" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:56:12</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>5.4059</v>
+      </c>
+      <c r="K118" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Sportybet, Betway</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:56:12</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>2.1632</v>
+      </c>
+      <c r="K119" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:56:12</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>3.9105</v>
+      </c>
+      <c r="K120" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Football.com, Betway</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:56:12</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Campeonato Brasileiro Série D</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="K121" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Football.com, Bangbet</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q121"/>
+  <dimension ref="A1:Q127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7733,10 +7733,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H116" t="n">
+        <v>4.5</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -7798,10 +7796,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H117" t="n">
+        <v>4.5</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -7863,10 +7859,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H118" t="n">
+        <v>1.5</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -7928,10 +7922,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H119" t="n">
+        <v>1.5</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -7993,10 +7985,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H120" t="n">
+        <v>1.5</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -8058,10 +8048,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H121" t="n">
+        <v>1.5</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -8087,6 +8075,396 @@
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:58:23</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Brasileiro Serie D</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>5.4059</v>
+      </c>
+      <c r="K122" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Sportybet, Betway</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:58:23</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Brasileiro Serie D</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>2.1632</v>
+      </c>
+      <c r="K123" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:58:23</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Brasileiro Serie D</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>3.9105</v>
+      </c>
+      <c r="K124" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Football.com, Betway</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:58:23</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Decisao PE</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>CS Sergipe SE</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Brasileiro Serie D</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>U1.5</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="K125" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Football.com, Bangbet</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:58:23</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K126" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L126" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-31 18:58:23</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K127" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L127" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q127"/>
+  <dimension ref="A1:Q129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8111,10 +8111,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H122" t="n">
+        <v>1.5</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -8176,10 +8174,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H123" t="n">
+        <v>1.5</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8241,10 +8237,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H124" t="n">
+        <v>1.5</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -8306,10 +8300,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H125" t="n">
+        <v>1.5</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -8371,10 +8363,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H126" t="n">
+        <v>4.5</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -8436,10 +8426,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H127" t="n">
+        <v>4.5</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -8465,6 +8453,136 @@
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr"/>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:00:31</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K128" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L128" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:00:31</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K129" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L129" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q129"/>
+  <dimension ref="A1:Q131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8489,10 +8489,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H128" t="n">
+        <v>4.5</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -8554,10 +8552,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H129" t="n">
+        <v>4.5</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -8583,6 +8579,136 @@
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:02:40</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K130" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L130" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:02:40</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K131" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L131" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q131"/>
+  <dimension ref="A1:Q133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8615,10 +8615,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H130" t="n">
+        <v>4.5</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -8680,10 +8678,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H131" t="n">
+        <v>4.5</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -8709,6 +8705,136 @@
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:04:48</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K132" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L132" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:04:48</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K133" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L133" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q133"/>
+  <dimension ref="A1:Q135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8741,10 +8741,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H132" t="n">
+        <v>4.5</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -8806,10 +8804,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H133" t="n">
+        <v>4.5</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -8835,6 +8831,136 @@
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:06:55</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K134" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L134" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:06:55</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K135" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L135" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q135"/>
+  <dimension ref="A1:Q137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8867,10 +8867,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H134" t="n">
+        <v>4.5</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -8932,10 +8930,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H135" t="n">
+        <v>4.5</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -8961,6 +8957,136 @@
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:09:05</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K136" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L136" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:09:05</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K137" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L137" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q137"/>
+  <dimension ref="A1:Q139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8993,10 +8993,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H136" t="n">
+        <v>4.5</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -9058,10 +9056,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H137" t="n">
+        <v>4.5</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -9087,6 +9083,136 @@
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:12:59</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K138" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L138" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:12:59</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K139" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L139" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q139"/>
+  <dimension ref="A1:Q141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9119,10 +9119,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H138" t="n">
+        <v>4.5</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -9184,10 +9182,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H139" t="n">
+        <v>4.5</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -9213,6 +9209,136 @@
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:13:53</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K140" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L140" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:13:53</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K141" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L141" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q141"/>
+  <dimension ref="A1:Q143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9245,10 +9245,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H140" t="n">
+        <v>4.5</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -9310,10 +9308,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H141" t="n">
+        <v>4.5</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -9339,6 +9335,136 @@
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:15:07</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K142" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L142" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:15:07</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K143" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L143" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q145"/>
+  <dimension ref="A1:Q147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9497,10 +9497,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H144" t="n">
+        <v>4.5</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -9562,10 +9560,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H145" t="n">
+        <v>4.5</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -9591,6 +9587,136 @@
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
     </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:21:31</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K146" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L146" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:21:31</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K147" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L147" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q147"/>
+  <dimension ref="A1:Q149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9623,10 +9623,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H146" t="n">
+        <v>4.5</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -9688,10 +9686,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H147" t="n">
+        <v>4.5</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -9717,6 +9713,136 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:22:27</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>18.5205</v>
+      </c>
+      <c r="K148" t="n">
+        <v>221.32</v>
+      </c>
+      <c r="L148" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:22:27</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>4.6762</v>
+      </c>
+      <c r="K149" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="L149" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q149"/>
+  <dimension ref="A1:Q151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9749,10 +9749,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H148" t="n">
+        <v>4.5</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -9814,10 +9812,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H149" t="n">
+        <v>4.5</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -9843,6 +9839,136 @@
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:32:14</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>25.928</v>
+      </c>
+      <c r="K150" t="n">
+        <v>309.84</v>
+      </c>
+      <c r="L150" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:32:14</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>11.2184</v>
+      </c>
+      <c r="K151" t="n">
+        <v>134.06</v>
+      </c>
+      <c r="L151" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q151"/>
+  <dimension ref="A1:Q153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9875,10 +9875,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H150" t="n">
+        <v>4.5</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -9940,10 +9938,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H151" t="n">
+        <v>4.5</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -9969,6 +9965,136 @@
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
     </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:33:21</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>25.928</v>
+      </c>
+      <c r="K152" t="n">
+        <v>309.84</v>
+      </c>
+      <c r="L152" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:33:21</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>11.2184</v>
+      </c>
+      <c r="K153" t="n">
+        <v>134.06</v>
+      </c>
+      <c r="L153" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q153"/>
+  <dimension ref="A1:Q155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10001,10 +10001,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H152" t="n">
+        <v>4.5</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -10066,10 +10064,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H153" t="n">
+        <v>4.5</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -10095,6 +10091,136 @@
       <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
     </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:34:22</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>25.928</v>
+      </c>
+      <c r="K154" t="n">
+        <v>309.84</v>
+      </c>
+      <c r="L154" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:34:22</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>11.2184</v>
+      </c>
+      <c r="K155" t="n">
+        <v>134.06</v>
+      </c>
+      <c r="L155" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q155"/>
+  <dimension ref="A1:Q157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10127,10 +10127,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H154" t="n">
+        <v>4.5</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -10192,10 +10190,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H155" t="n">
+        <v>4.5</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -10221,6 +10217,136 @@
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:36:30</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>25.928</v>
+      </c>
+      <c r="K156" t="n">
+        <v>309.84</v>
+      </c>
+      <c r="L156" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-05-31 19:36:30</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>11.2184</v>
+      </c>
+      <c r="K157" t="n">
+        <v>134.06</v>
+      </c>
+      <c r="L157" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1370,10 +1370,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H15" t="n">
+        <v>4.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1399,6 +1397,136 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-31 22:07:44</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="K16" t="n">
+        <v>296.32</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-31 22:07:44</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>LigaPro Primera A</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="K17" t="n">
+        <v>74.72</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>22Bet, Betway</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1433,10 +1433,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H16" t="n">
+        <v>4.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1498,10 +1496,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H17" t="n">
+        <v>4.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1527,6 +1523,372 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:17:49</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>8.5281</v>
+      </c>
+      <c r="K18" t="n">
+        <v>136.45</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:17:49</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>15.2881</v>
+      </c>
+      <c r="K19" t="n">
+        <v>244.61</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet, MSport</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:17:49</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>13.805</v>
+      </c>
+      <c r="K20" t="n">
+        <v>220.88</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>22Bet, 22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:17:49</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>20.8938</v>
+      </c>
+      <c r="K21" t="n">
+        <v>334.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>22Bet, 22Bet, MSport</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:17:49</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>7.3431</v>
+      </c>
+      <c r="K22" t="n">
+        <v>117.49</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>22Bet, MSport, Sportybet</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:17:49</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="K23" t="n">
+        <v>224.48</v>
+      </c>
+      <c r="L23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>22Bet, MSport, MSport</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1889,6 +1889,128 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:19:58</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>15.2881</v>
+      </c>
+      <c r="K24" t="n">
+        <v>244.61</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet, MSport</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:19:58</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>7.3431</v>
+      </c>
+      <c r="K25" t="n">
+        <v>117.49</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>22Bet, MSport, Sportybet</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2011,6 +2011,128 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:22:07</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>15.2881</v>
+      </c>
+      <c r="K26" t="n">
+        <v>244.61</v>
+      </c>
+      <c r="L26" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet, MSport</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:22:07</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>7.3431</v>
+      </c>
+      <c r="K27" t="n">
+        <v>117.49</v>
+      </c>
+      <c r="L27" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>22Bet, MSport, Sportybet</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2133,6 +2133,128 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:24:15</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>15.2881</v>
+      </c>
+      <c r="K28" t="n">
+        <v>244.61</v>
+      </c>
+      <c r="L28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet, MSport</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:24:15</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>7.3431</v>
+      </c>
+      <c r="K29" t="n">
+        <v>117.49</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>22Bet, MSport, Sportybet</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2255,6 +2255,128 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:26:24</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>15.2881</v>
+      </c>
+      <c r="K30" t="n">
+        <v>244.61</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet, MSport</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:26:24</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>7.3431</v>
+      </c>
+      <c r="K31" t="n">
+        <v>117.49</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>22Bet, MSport, Sportybet</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2377,6 +2377,128 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:28:33</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>15.2881</v>
+      </c>
+      <c r="K32" t="n">
+        <v>244.61</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet, MSport</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:28:33</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>7.3431</v>
+      </c>
+      <c r="K33" t="n">
+        <v>117.49</v>
+      </c>
+      <c r="L33" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>22Bet, MSport, Sportybet</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2499,6 +2499,372 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:30:41</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>8.5283</v>
+      </c>
+      <c r="K34" t="n">
+        <v>102.34</v>
+      </c>
+      <c r="L34" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:30:41</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="K35" t="n">
+        <v>183.48</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet, MSport</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:30:41</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>13.8058</v>
+      </c>
+      <c r="K36" t="n">
+        <v>165.67</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>22Bet, 22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:30:41</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>20.895</v>
+      </c>
+      <c r="K37" t="n">
+        <v>250.74</v>
+      </c>
+      <c r="L37" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>22Bet, 22Bet, MSport</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:30:41</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>7.3433</v>
+      </c>
+      <c r="K38" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="L38" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>22Bet, MSport, Sportybet</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:30:41</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="K39" t="n">
+        <v>168.36</v>
+      </c>
+      <c r="L39" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>22Bet, MSport, MSport</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2865,6 +2865,128 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:34:58</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>5.4575</v>
+      </c>
+      <c r="K40" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="L40" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>MSport, Sportybet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:34:58</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>9.664999999999999</v>
+      </c>
+      <c r="K41" t="n">
+        <v>115.98</v>
+      </c>
+      <c r="L41" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>MSport, MSport, Sportybet</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2987,6 +2987,189 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:37:06</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>2.5567</v>
+      </c>
+      <c r="K42" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="L42" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>22Bet, Sportybet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:37:06</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>5.1642</v>
+      </c>
+      <c r="K43" t="n">
+        <v>61.97</v>
+      </c>
+      <c r="L43" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>22Bet, 22Bet, Sportybet</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-01 06:37:06</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Kisumu All Stars FC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Migori Youth FC</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Super League</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1.5292</v>
+      </c>
+      <c r="K44" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="L44" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>22Bet, MSport, Sportybet</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3170,6 +3170,189 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:28:50</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K45" t="n">
+        <v>15</v>
+      </c>
+      <c r="L45" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Betway, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:28:50</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>1.1933</v>
+      </c>
+      <c r="K46" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="L46" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1xBet, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:28:50</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0.09420000000000001</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L47" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Bangbet, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3353,6 +3353,250 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:44:39</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1.2842</v>
+      </c>
+      <c r="K48" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="L48" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Sportybet, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:44:39</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>4.7292</v>
+      </c>
+      <c r="K49" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="L49" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Betway, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:44:39</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>2.4125</v>
+      </c>
+      <c r="K50" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="L50" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>1xBet, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:44:39</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>2.4708</v>
+      </c>
+      <c r="K51" t="n">
+        <v>29.65</v>
+      </c>
+      <c r="L51" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Bangbet, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3597,6 +3597,128 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:46:54</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Zvezda St Petersburg</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>FC Irkutsk 2020</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Russian Championship</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>League 2. Division B. Group 2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Football.com, Sportybet, 1xBet</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:46:54</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Zvezda St Petersburg</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>FC Irkutsk 2020</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Russian Championship</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>League 2. Division B. Group 2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>1.0133</v>
+      </c>
+      <c r="K53" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Football.com, MSport, 1xBet</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3719,6 +3719,67 @@
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:49:09</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Zvezda St Petersburg</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>FC Irkutsk 2020</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Russian Championship</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>League 2. Division B. Group 2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0.6208</v>
+      </c>
+      <c r="K54" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Football.com, MSport, 1xBet</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3780,6 +3780,67 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:23:41</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>1.4733</v>
+      </c>
+      <c r="K55" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="L55" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Betway, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3841,6 +3841,67 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:12:49</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>TPV/2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Toip-49</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kolmonen</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>GG/NG</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>36.9958</v>
+      </c>
+      <c r="K56" t="n">
+        <v>443.95</v>
+      </c>
+      <c r="L56" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q56"/>
+  <dimension ref="A1:Q57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3902,6 +3902,67 @@
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:17:15</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>TPV/2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Toip-49</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Kolmonen</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>GG/NG</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>36.9947</v>
+      </c>
+      <c r="K57" t="n">
+        <v>351.45</v>
+      </c>
+      <c r="L57" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:Q58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3963,6 +3963,67 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:19:30</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0.4158</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L58" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Betway, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4024,6 +4024,67 @@
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:24:03</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>TPV/2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Toip-49</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Kolmonen</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>GG/NG</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>48.1579</v>
+      </c>
+      <c r="K59" t="n">
+        <v>457.5</v>
+      </c>
+      <c r="L59" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4085,6 +4085,197 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:26:17</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Vasa IFK</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>KPV/Akatemia</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Kolmonen. Division 3</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>2.6368</v>
+      </c>
+      <c r="K60" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="L60" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>MSport, 1xBet</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:26:17</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Vasa IFK</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>KPV/Akatemia</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kolmonen. Division 3</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0.7095</v>
+      </c>
+      <c r="K61" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="L61" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Bangbet, 1xBet</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:26:17</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>TPV/2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Toip-49</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Kolmonen</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>GG/NG</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>44.6063</v>
+      </c>
+      <c r="K62" t="n">
+        <v>423.76</v>
+      </c>
+      <c r="L62" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:Q66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4121,10 +4121,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H60" t="n">
+        <v>4.5</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -4186,10 +4184,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H61" t="n">
+        <v>4.5</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -4276,6 +4272,262 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:28:32</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Vasa IFK</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>KPV/Akatemia</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Kolmonen. Division 3</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>1.3884</v>
+      </c>
+      <c r="K63" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="L63" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:28:32</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Vasa IFK</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>KPV/Akatemia</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Kolmonen. Division 3</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>4.3274</v>
+      </c>
+      <c r="K64" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="L64" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>MSport, 1xBet</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:28:32</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Vasa IFK</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>KPV/Akatemia</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Kolmonen. Division 3</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>O4.5</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>2.3684</v>
+      </c>
+      <c r="K65" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L65" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Bangbet, 1xBet</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:28:32</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>TPV/2</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Toip-49</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kolmonen</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>GG/NG</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>47.1432</v>
+      </c>
+      <c r="K66" t="n">
+        <v>447.86</v>
+      </c>
+      <c r="L66" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4308,10 +4308,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H63" t="n">
+        <v>4.5</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -4373,10 +4371,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H64" t="n">
+        <v>4.5</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -4438,10 +4434,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="H65" t="n">
+        <v>4.5</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -4528,6 +4522,136 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:30:47</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Vasa IFK</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>KPV/Akatemia</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Kolmonen. Division 3</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>O5.5</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>5.5179</v>
+      </c>
+      <c r="K67" t="n">
+        <v>52.42</v>
+      </c>
+      <c r="L67" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:30:47</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Vasa IFK</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>KPV/Akatemia</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Kolmonen. Division 3</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Over/Under</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>O5.5</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0.8632</v>
+      </c>
+      <c r="K68" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L68" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>MSport, 1xBet</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:Q69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4558,10 +4558,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
+      <c r="H67" t="n">
+        <v>5.5</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4623,10 +4621,8 @@
           <t>Over/Under</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
+      <c r="H68" t="n">
+        <v>5.5</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4652,6 +4648,67 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:33:09</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>TPV/2</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Toip-49</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Kolmonen</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>GG/NG</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>42.0695</v>
+      </c>
+      <c r="K69" t="n">
+        <v>399.66</v>
+      </c>
+      <c r="L69" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:Q70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4709,6 +4709,67 @@
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:39:49</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>TPV/2</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Toip-49</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Kolmonen</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>GG/NG</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>31.9211</v>
+      </c>
+      <c r="K70" t="n">
+        <v>303.25</v>
+      </c>
+      <c r="L70" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:Q71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4770,6 +4770,67 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:44:13</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TPV/2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Toip-49</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Kolmonen</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>GG/NG</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>42.0695</v>
+      </c>
+      <c r="K71" t="n">
+        <v>399.66</v>
+      </c>
+      <c r="L71" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4831,6 +4831,67 @@
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:51:00</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>TPV/2</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Toip-49</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Kolmonen</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>GG/NG</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>44.6063</v>
+      </c>
+      <c r="K72" t="n">
+        <v>423.76</v>
+      </c>
+      <c r="L72" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4892,6 +4892,67 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:04:25</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>TPV/2</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Toip-49</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Kolmonen</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>GG/NG</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>39.5316</v>
+      </c>
+      <c r="K73" t="n">
+        <v>375.55</v>
+      </c>
+      <c r="L73" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4953,6 +4953,67 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:08:56</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Vilavelhense FC ES</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Vitoria FC ES</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Copa Espirito Santo</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.1347</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L74" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Betway, 22Bet, 22Bet</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5014,6 +5014,67 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:13:25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>TPV/2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Toip-49</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Kolmonen</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>GG/NG</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>47.1432</v>
+      </c>
+      <c r="K75" t="n">
+        <v>447.86</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5075,6 +5075,311 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:15:41</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>0.6737</v>
+      </c>
+      <c r="K76" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L76" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Sportybet, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:15:41</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>3.3768</v>
+      </c>
+      <c r="K77" t="n">
+        <v>32.08</v>
+      </c>
+      <c r="L77" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Betway, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:15:41</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>1.2305</v>
+      </c>
+      <c r="K78" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="L78" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>22Bet, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:15:41</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>1.0632</v>
+      </c>
+      <c r="K79" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L79" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>MSport, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:15:41</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K80" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="L80" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Bangbet, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5380,6 +5380,67 @@
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:17:52</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TPV/2</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Toip-49</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Kolmonen</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>GG/NG</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>34.4579</v>
+      </c>
+      <c r="K81" t="n">
+        <v>327.35</v>
+      </c>
+      <c r="L81" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5441,6 +5441,372 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:24:37</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>0.6707</v>
+      </c>
+      <c r="K82" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="L82" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Sportybet, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:24:37</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>3.3773</v>
+      </c>
+      <c r="K83" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="L83" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Betway, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:24:37</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>1.232</v>
+      </c>
+      <c r="K84" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="L84" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>22Bet, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:24:37</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>1.064</v>
+      </c>
+      <c r="K85" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="L85" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>MSport, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:24:37</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Int. Friendly Games</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>2.3187</v>
+      </c>
+      <c r="K86" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="L86" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Bangbet, Betway, 1xBet</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:24:37</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TPV/2</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Toip-49</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Kolmonen</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>GG/NG</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>34.4573</v>
+      </c>
+      <c r="K87" t="n">
+        <v>258.43</v>
+      </c>
+      <c r="L87" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:Q88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5807,6 +5807,67 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:31:44</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>TPV/2</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Toip-49</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Kolmonen</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>GG/NG</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>42.068</v>
+      </c>
+      <c r="K88" t="n">
+        <v>315.51</v>
+      </c>
+      <c r="L88" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Sportybet, Bangbet</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/quasi_arb_ml.xlsx
+++ b/data/quasi_arb_ml.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q88"/>
+  <dimension ref="A1:Q89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5868,6 +5868,67 @@
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:33:59</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>TPV/2</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Toip-49</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Kolmonen</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>GG/NG</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>39.532</v>
+      </c>
+      <c r="K89" t="n">
+        <v>296.49</v>
+      </c>
+      <c r="L89" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Football.com, Bangbet</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
